--- a/lib/output/results_consolidados.xlsx
+++ b/lib/output/results_consolidados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,18 +461,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[21, 13, 21, 31, 14]</t>
+          <t>[12, 18, 18, 12, 19]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.57577825945877</v>
+        <v>51.9188193487698</v>
       </c>
       <c r="D2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>205.76 segundos</t>
+          <t>217.96 segundos</t>
         </is>
       </c>
     </row>
@@ -482,18 +482,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[21, 8, 21, 31, 14]</t>
+          <t>[12, 18, 18, 12, 19]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.57577825945873</v>
+        <v>51.9188193487698</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>228.98 segundos</t>
+          <t>189.98 segundos</t>
         </is>
       </c>
     </row>
@@ -503,60 +503,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[21, 8, 21, 2, 14]</t>
+          <t>[12, 18, 18, 12, 19]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.57577825945872</v>
+        <v>51.9188193487698</v>
       </c>
       <c r="D4" t="n">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>238.80 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[21, 8, 21, 2, 14]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>50.57577825945872</v>
-      </c>
-      <c r="D5" t="n">
-        <v>105</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>267.61 segundos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[21, 27, 21, 21, 14]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>49.13545004407987</v>
-      </c>
-      <c r="D6" t="n">
-        <v>187</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>280.44 segundos</t>
+          <t>185.19 segundos</t>
         </is>
       </c>
     </row>
